--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,10 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Space</t>
         </is>
@@ -455,19 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.74305</v>
+        <v>17.0871</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30301</v>
+        <v>16.06973</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76437</v>
+        <v>16.42635</v>
       </c>
       <c r="F2" t="n">
-        <v>21.86224</v>
+        <v>21.86812</v>
       </c>
       <c r="G2" t="n">
-        <v>34.32141</v>
+        <v>21.23937</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34.82671</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.55335</v>
+        <v>16.69942</v>
       </c>
       <c r="D3" t="n">
-        <v>16.1865</v>
+        <v>15.9183</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55079</v>
+        <v>16.34647</v>
       </c>
       <c r="F3" t="n">
-        <v>21.91901</v>
+        <v>22.41978</v>
       </c>
       <c r="G3" t="n">
-        <v>34.55486</v>
+        <v>21.65211</v>
+      </c>
+      <c r="H3" t="n">
+        <v>34.45813</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.77746</v>
+        <v>16.99396</v>
       </c>
       <c r="D4" t="n">
-        <v>16.21997</v>
+        <v>16.15677</v>
       </c>
       <c r="E4" t="n">
-        <v>16.53764</v>
+        <v>16.41</v>
       </c>
       <c r="F4" t="n">
-        <v>22.20101</v>
+        <v>22.06716</v>
       </c>
       <c r="G4" t="n">
-        <v>34.1516</v>
+        <v>21.76735</v>
+      </c>
+      <c r="H4" t="n">
+        <v>34.22644</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.64789</v>
+        <v>16.65287</v>
       </c>
       <c r="D5" t="n">
-        <v>16.16275</v>
+        <v>16.01673</v>
       </c>
       <c r="E5" t="n">
-        <v>16.21612</v>
+        <v>16.42925</v>
       </c>
       <c r="F5" t="n">
-        <v>22.20882</v>
+        <v>22.15041</v>
       </c>
       <c r="G5" t="n">
-        <v>34.30217</v>
+        <v>21.74111</v>
+      </c>
+      <c r="H5" t="n">
+        <v>34.15205</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.73233</v>
+        <v>16.78481</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9126</v>
+        <v>15.92273</v>
       </c>
       <c r="E6" t="n">
-        <v>16.36887</v>
+        <v>16.72397</v>
       </c>
       <c r="F6" t="n">
-        <v>21.749</v>
+        <v>21.5802</v>
       </c>
       <c r="G6" t="n">
-        <v>34.38995</v>
+        <v>21.88746</v>
+      </c>
+      <c r="H6" t="n">
+        <v>34.2228</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.80923</v>
+        <v>17.04317</v>
       </c>
       <c r="D7" t="n">
-        <v>16.30696</v>
+        <v>16.15909</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56855</v>
+        <v>16.42507</v>
       </c>
       <c r="F7" t="n">
-        <v>21.65481</v>
+        <v>22.25221</v>
       </c>
       <c r="G7" t="n">
-        <v>34.5692</v>
+        <v>22.123</v>
+      </c>
+      <c r="H7" t="n">
+        <v>34.81707</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.76483</v>
+        <v>16.804</v>
       </c>
       <c r="D8" t="n">
-        <v>16.35184</v>
+        <v>16.17753</v>
       </c>
       <c r="E8" t="n">
-        <v>16.76567</v>
+        <v>16.54303</v>
       </c>
       <c r="F8" t="n">
-        <v>21.57582</v>
+        <v>21.7066</v>
       </c>
       <c r="G8" t="n">
-        <v>33.81249</v>
+        <v>21.76739</v>
+      </c>
+      <c r="H8" t="n">
+        <v>34.73334</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.06777</v>
+        <v>16.90546</v>
       </c>
       <c r="D9" t="n">
-        <v>16.17199</v>
+        <v>15.58143</v>
       </c>
       <c r="E9" t="n">
-        <v>16.73708</v>
+        <v>16.37923</v>
       </c>
       <c r="F9" t="n">
-        <v>21.57956</v>
+        <v>22.02031</v>
       </c>
       <c r="G9" t="n">
-        <v>33.77234</v>
+        <v>22.2596</v>
+      </c>
+      <c r="H9" t="n">
+        <v>34.50258</v>
       </c>
     </row>
     <row r="10">
@@ -631,281 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.1476</v>
+        <v>16.78238</v>
       </c>
       <c r="D10" t="n">
-        <v>16.04612</v>
+        <v>16.10623</v>
       </c>
       <c r="E10" t="n">
-        <v>16.44198</v>
+        <v>16.42802</v>
       </c>
       <c r="F10" t="n">
-        <v>22.34835</v>
+        <v>21.84638</v>
       </c>
       <c r="G10" t="n">
-        <v>34.21493</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>17.18433</v>
-      </c>
-      <c r="D12" t="n">
-        <v>16.96998</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.78908</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41.0554</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05013</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.85277</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>17.06429</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.46573</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.93184</v>
-      </c>
-      <c r="F13" t="n">
-        <v>42.27761</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05195</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.83862</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>17.32433</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.51318</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.98534</v>
-      </c>
-      <c r="F14" t="n">
-        <v>42.07044</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0509</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.79791</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>17.0403</v>
-      </c>
-      <c r="D15" t="n">
-        <v>16.58233</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.92889</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.57239</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.82657</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>16.85471</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16.63898</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.72621</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.77678</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05035</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.80492</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>16.76712</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.7759</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.55333</v>
-      </c>
-      <c r="F17" t="n">
-        <v>42.31669</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05003</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.81888</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>16.8482</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.78987</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.80417</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42.96098</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05119</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.81553</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>17.27019</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.76114</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.67168</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.4676</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.76963</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>16.88266</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.27507</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.83895</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.53419</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05174</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.82641</v>
+        <v>21.76299</v>
+      </c>
+      <c r="H10" t="n">
+        <v>33.90602</v>
       </c>
     </row>
   </sheetData>
